--- a/data/trans_dic/IP44C$impuestos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 9,85</t>
+          <t>0,76; 10,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 15,93</t>
+          <t>1,96; 16,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 10,49</t>
+          <t>2,15; 9,83</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,56</t>
+          <t>1,05; 3,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,89</t>
+          <t>0,31; 1,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,12</t>
+          <t>0,84; 2,26</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,2</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,85</t>
+          <t>1,09; 2,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,05</t>
+          <t>0,59; 2,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,19</t>
+          <t>0,94; 2,16</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5992</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>396; 5260</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1178; 9853</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2418; 11036</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9024</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13121</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4746; 16071</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1540; 9662</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7989; 21596</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6531</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12105</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8372</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20477</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7131; 19227</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4420; 15600</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>13156; 30099</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$impuestos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 10,08</t>
+          <t>0,76; 10,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 16,4</t>
+          <t>2,52; 16,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 9,83</t>
+          <t>2,27; 10,1</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,57</t>
+          <t>1,08; 3,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,92</t>
+          <t>0,31; 1,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,26</t>
+          <t>0,81; 2,07</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,95</t>
+          <t>1,05; 2,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,1</t>
+          <t>0,58; 1,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,16</t>
+          <t>0,98; 2,21</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>396; 5260</t>
+          <t>397; 5268</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1178; 9853</t>
+          <t>1515; 9954</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2418; 11036</t>
+          <t>2552; 11347</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4746; 16071</t>
+          <t>4860; 15279</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1540; 9662</t>
+          <t>1545; 9313</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7989; 21596</t>
+          <t>7777; 19771</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6178</t>
+          <t>0; 5837</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6531</t>
+          <t>0; 6192</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7131; 19227</t>
+          <t>6830; 19183</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4420; 15600</t>
+          <t>4295; 14694</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13156; 30099</t>
+          <t>13705; 30855</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$impuestos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 10,09</t>
+          <t>2,68; 16,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 16,56</t>
+          <t>0,74; 10,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 10,1</t>
+          <t>2,4; 11,25</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,39</t>
+          <t>0,28; 1,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,85</t>
+          <t>1,17; 3,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,07</t>
+          <t>0,85; 2,25</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,94</t>
+          <t>0,54; 2,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,97</t>
+          <t>1,2; 3,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,21</t>
+          <t>1,04; 2,27</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5689</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>397; 5268</t>
+          <t>1470; 9069</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1515; 9954</t>
+          <t>331; 4566</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2552; 11347</t>
+          <t>2379; 11166</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>12783</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4860; 15279</t>
+          <t>1290; 9188</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1545; 9313</t>
+          <t>4927; 16283</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7777; 19771</t>
+          <t>7571; 19935</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1596</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5837</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6722</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6192</t>
+          <t>0; 6846</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>20068</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6830; 19183</t>
+          <t>3669; 14550</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4295; 14694</t>
+          <t>7390; 18687</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13705; 30855</t>
+          <t>13498; 29527</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$impuestos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$impuestos_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,68; 16,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,74; 10,28</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,4; 11,25</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 1,99</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,17; 3,85</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,85; 2,25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,49</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 2,13</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 3,03</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,04; 2,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.07433511877202083</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.03633427087299271</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.05732672542427499</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4075</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1614</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.02681493819036162</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.007443839014395089</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.02397391785827417</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1470; 9069</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>331; 4566</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2379; 11166</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1654183591445013</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1027788718470806</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1125088511484802</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.007930883997191371</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.02154966376349781</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01443289991802539</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3671</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9112</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12783</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.002787150646266745</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.01165224295173269</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.008548141122772569</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1290; 9188</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4927; 16283</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7571; 19935</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.01985261655220023</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.03850822264422756</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.02250850587203856</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,47 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.01066481965971692</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.005065048389949166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1596</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1596</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 6722</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 6846</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>0.04492046215967527</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.02172989185991995</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +713,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.01133986487354178</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01997401602472994</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01543716156612405</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>7746</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>12322</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>20068</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.005370905468980438</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01197890024747028</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.01038343752593734</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>3669; 14550</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>7390; 18687</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>13498; 29527</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.02130044680734736</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.03029072834385894</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.02271324652790862</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +777,372 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de impuestos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4075</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1614</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5689</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1470</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>331</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>9069</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>4566</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>11166</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3671</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>9112</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>12783</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4927</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>7571</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>9188</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>16283</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>19935</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1596</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="n">
+        <v>6722</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>6846</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>7746</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>12322</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>20068</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3669</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>7390</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>13498</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>14550</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>18687</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>29527</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>